--- a/additional_material/income.xlsx
+++ b/additional_material/income.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sassa\MDS2025\ASDA_2025_Group_3_Porfolio\additional_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D0483E7-8F78-41C4-9187-027A267683D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A0A337-6B77-49B3-9BEA-0B9E96A450A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">composition!$A$1:$D$2080</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'List of economies'!$A$1:$B$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'List of economies'!$A$1:$B$223</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8768" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8770" uniqueCount="565">
   <si>
     <t>Economy</t>
   </si>
@@ -1737,6 +1737,9 @@
   </si>
   <si>
     <t>Yemen</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B225"/>
+  <dimension ref="A1:B226"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.77734375" bestFit="1" customWidth="1"/>
@@ -2666,7 +2669,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>547</v>
+        <v>116</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>9</v>
@@ -2674,7 +2677,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>9</v>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>543</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>9</v>
@@ -2690,23 +2693,23 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>25</v>
@@ -2714,7 +2717,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>25</v>
@@ -2722,31 +2725,31 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>560</v>
+        <v>128</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>560</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>21</v>
@@ -2754,23 +2757,23 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>21</v>
@@ -2778,31 +2781,31 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>9</v>
@@ -2810,23 +2813,23 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>21</v>
@@ -2834,15 +2837,15 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>9</v>
@@ -2850,23 +2853,23 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>9</v>
@@ -2874,7 +2877,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>9</v>
@@ -2882,39 +2885,39 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>21</v>
@@ -2922,15 +2925,15 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>25</v>
@@ -2938,7 +2941,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>25</v>
@@ -2946,23 +2949,23 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>550</v>
+        <v>184</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>550</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>9</v>
@@ -2970,31 +2973,31 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>556</v>
+        <v>194</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>556</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>4</v>
@@ -3002,15 +3005,15 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>9</v>
@@ -3018,79 +3021,79 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>557</v>
+        <v>204</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>206</v>
+        <v>557</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>15</v>
@@ -3098,7 +3101,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>546</v>
+        <v>220</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>15</v>
@@ -3106,39 +3109,39 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>224</v>
+        <v>546</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>552</v>
+        <v>226</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>230</v>
+        <v>558</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>15</v>
@@ -3146,31 +3149,31 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>21</v>
@@ -3178,23 +3181,23 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>9</v>
@@ -3202,7 +3205,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>9</v>
@@ -3210,23 +3213,23 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>21</v>
@@ -3234,55 +3237,55 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B130" s="8" t="s">
         <v>21</v>
@@ -3290,31 +3293,31 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>9</v>
@@ -3322,87 +3325,87 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B145" s="8" t="s">
         <v>15</v>
@@ -3410,23 +3413,23 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B148" s="8" t="s">
         <v>21</v>
@@ -3434,55 +3437,55 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>551</v>
+        <v>302</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>306</v>
+        <v>551</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>312</v>
-      </c>
-      <c r="B153" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B153" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>555</v>
-      </c>
-      <c r="B154" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B154" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>314</v>
+        <v>555</v>
       </c>
       <c r="B155" s="8" t="s">
         <v>4</v>
@@ -3490,31 +3493,31 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B159" s="8" t="s">
         <v>25</v>
@@ -3522,23 +3525,23 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>9</v>
@@ -3546,31 +3549,31 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>548</v>
+        <v>334</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>9</v>
@@ -3578,71 +3581,71 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>338</v>
+        <v>548</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B175" s="8" t="s">
         <v>21</v>
@@ -3650,31 +3653,31 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>362</v>
+        <v>564</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>9</v>
@@ -3682,23 +3685,23 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>362</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>364</v>
       </c>
-      <c r="B180" s="8" t="s">
+      <c r="B181" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="15" t="s">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="B181" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>367</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>21</v>
@@ -3706,7 +3709,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>21</v>
@@ -3714,31 +3717,31 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B187" s="8" t="s">
         <v>25</v>
@@ -3746,7 +3749,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B188" s="8" t="s">
         <v>25</v>
@@ -3754,7 +3757,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>25</v>
@@ -3762,31 +3765,31 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>9</v>
@@ -3794,47 +3797,47 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>562</v>
+        <v>389</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>395</v>
+        <v>544</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>15</v>
@@ -3842,47 +3845,47 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>545</v>
+        <v>405</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>409</v>
+        <v>545</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>549</v>
+        <v>409</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>413</v>
+        <v>549</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>9</v>
@@ -3890,119 +3893,119 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>554</v>
+        <v>433</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>437</v>
+        <v>554</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>563</v>
+        <v>441</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>4</v>
@@ -4010,37 +4013,45 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>445</v>
+        <v>563</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B222" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B224" s="10"/>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>447</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B225" s="10"/>
     </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B226" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B222" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A222">
-    <sortCondition ref="A2:A222"/>
+  <autoFilter ref="A1:B223" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A223">
+    <sortCondition ref="A2:A223"/>
   </sortState>
-  <conditionalFormatting sqref="B224:B225">
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  <conditionalFormatting sqref="B225:B226">
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -33181,13 +33192,13 @@
   </sheetData>
   <autoFilter ref="A1:D2080" xr:uid="{E7D19960-BA51-4EF8-A877-5D4B3211E652}"/>
   <conditionalFormatting sqref="C1367:C1469">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1470">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1809:C1858">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
